--- a/Courses/Term 3/QAM-III/801 - DATA - S&P500 INDEX.xlsx
+++ b/Courses/Term 3/QAM-III/801 - DATA - S&P500 INDEX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suranjandas/Desktop/SIRMAUR. IIM .. Nov 14 2025/T1 - Non Linear Programming/SOLN.. for SD/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MBA\Courses\Term 3\QAM-III\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0796A4B5-07C3-CD47-831F-6AA6FAA6F45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFD9437-E486-42A2-A8C8-83A9564308CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="740" windowWidth="27640" windowHeight="16760" xr2:uid="{B2BED8D6-8C7E-0E42-9D17-93C443EBC8CA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B2BED8D6-8C7E-0E42-9D17-93C443EBC8CA}"/>
   </bookViews>
   <sheets>
     <sheet name="Making an NDEX Fund p345" sheetId="3" r:id="rId1"/>
@@ -211,9 +211,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -251,7 +251,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -357,7 +357,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -499,7 +499,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -508,13 +508,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C43CC6F-7E8F-7643-8DD9-676D7BF3B446}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="1" max="1" width="23.296875" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -526,7 +526,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
     </row>
-    <row r="2" spans="1:8" ht="3" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -536,7 +536,7 @@
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -550,7 +550,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -564,7 +564,7 @@
         <v>0.2525</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -578,7 +578,7 @@
         <v>0.24929999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -592,7 +592,7 @@
         <v>0.24410000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -606,7 +606,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>25</v>
       </c>
@@ -618,7 +618,7 @@
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -628,7 +628,7 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -638,7 +638,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
@@ -659,7 +659,7 @@
       </c>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -680,7 +680,7 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -701,7 +701,7 @@
       </c>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -722,7 +722,7 @@
       </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -743,7 +743,7 @@
       </c>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
       </c>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -785,7 +785,7 @@
       </c>
       <c r="H18" s="1"/>
     </row>
-    <row r="20" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>7</v>
       </c>
@@ -805,17 +805,17 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>26</v>
       </c>
